--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/jun-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>14.164.209-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>77.367.722-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1712,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1777,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2411,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2476,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2541,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2606,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2736,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2923,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2832,7 +2940,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1346281-99-CM25</t>
+          <t>1960-39-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,43 +2965,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7449.05</v>
+        <v>20281.13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1960-39-CM25</t>
+          <t>3970-32-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2918,43 +3030,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>20281.13</v>
+        <v>6868.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3970-32-CM25</t>
+          <t>1346281-99-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,17 +3095,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3002,14 +3118,18 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6868.93</v>
+        <v>7449.05</v>
       </c>
     </row>
     <row r="43">
@@ -3063,7 +3183,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3309,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3374,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3500,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3565,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3630,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3756,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3625,7 +3773,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1426098-160-CM25</t>
+          <t>1057062-226-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,17 +3798,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3673,20 +3821,24 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>23292.34</v>
+        <v>13255.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057062-226-CM25</t>
+          <t>1426098-160-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,17 +3863,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3734,14 +3886,18 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>13255.47</v>
+        <v>23292.34</v>
       </c>
     </row>
     <row r="55">
@@ -3795,7 +3951,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3808,7 +3968,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2945-590-CM25</t>
+          <t>2421-3990-SE25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,43 +3993,47 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>FRANCISCO ANTONIO PALACIOS MUÑOZ</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>14.164.209-K</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>9365.59</v>
+        <v>1267.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2421-3979-CM25</t>
+          <t>2945-590-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,97 +4058,170 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FRANCISCO ANTONIO PALACIOS MUÑOZ</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>14.164.209-K</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7126.39</v>
+        <v>9365.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>2421-3979-CM25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.256.900-8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>FRANCISCO ANTONIO PALACIOS MUÑOZ</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>14.164.209-K</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>7126.39</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>2324-926-CM25</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2239-3-LR23</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>jun-2025</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>69.220.100-0</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="n">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>21629.88</v>
       </c>
     </row>
